--- a/docs/jp/07_進捗報告書.xlsx
+++ b/docs/jp/07_進捗報告書.xlsx
@@ -156,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,7 +202,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -698,15 +701,9 @@
       <c r="C11" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="C11:E11"/>
+  <mergeCells count="2">
+    <mergeCell ref="B2:E3"/>
     <mergeCell ref="B4:E4"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="B2:E3"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C10:E10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -727,15 +724,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -759,18 +754,8 @@
           <t>作成</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
-        <is>
-          <t>確認</t>
-        </is>
-      </c>
-      <c r="F1" s="6" t="inlineStr">
-        <is>
-          <t>承認</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+    </row>
+    <row r="2" ht="16.5" customHeight="1">
       <c r="A2" s="7" t="inlineStr">
         <is>
           <t>v0.5</t>
@@ -789,16 +774,6 @@
       <c r="D2" s="7" t="inlineStr">
         <is>
           <t>(担当部門)</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>(日本側ネイティブ確認担当指名待ち)</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>Bojiang Zhang</t>
         </is>
       </c>
     </row>
@@ -1049,11 +1024,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1063,205 +1039,177 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="18" customHeight="1">
+    <row r="2">
       <c r="B2" s="17" t="inlineStr">
         <is>
           <t>1.1 本報告書の位置づけ</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="B3" s="17" t="inlineStr">
+    <row r="3">
+      <c r="C3" s="18" t="inlineStr">
         <is>
           <t>本書は, iTMS 株式会社向け納品ドキュメント整備作業 (以下「本作業」と表記する) の進捗を中間段階で報告するものである。納品形式は Excel (.xlsx) を主体とし, 受信者向け文書 7 件 + 用語集 1 件 = 計 8 件を整備対象とする。</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="B4" s="17" t="inlineStr">
+    <row r="4">
+      <c r="C4" s="18" t="inlineStr">
         <is>
           <t>本中間版 (v0.5) では, 工程順序の根拠となる先頭 2 件 (要件定義書 / 基本設計書) を確定状態 (v1.0) で提出する。残 5 件は仕上げ段階 (2026-05-初旬 - 中旬) で順次提出予定である。</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>出典: docs/jp/PLAN.md §0 + §1 文書一覧。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="B6" s="17" t="inlineStr">
-        <is>
           <t>1.2 主要マイルストーン</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+    <row r="6">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>下表に主要マイルストーンを示す。</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+    <row r="7">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-29: 基本骨格構築 (第 0 段階) 完了</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+    <row r="8">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-29: 用語調研 (第 0.5 段階) 完了 (用語写像辞書 v0.3 を独立確認 3 回で確定)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+    <row r="9">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-29: Excel 基盤構築 (第 0.7 段階) 完了 (スタイル指針 / 表紙統一様式 / 生成処理)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+    <row r="10">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-29: 要件定義書 v1.0 確定 (第 1 段階 第 1 着手)</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+    <row r="11">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-29: 基本設計書 v1.0 確定 (第 1 段階 第 2 着手)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+    <row r="12">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>- 2026-04-30: 中間版進捗報告書 v0.5 作成 + 中間提出</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+    <row r="13">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>- 2026-05-初旬 (予定): 運用保守マニュアル / 試験結果報告書 v1.0 (並列着手)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+    <row r="14">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>- 2026-05-中旬 (予定): 詳細設計書 / トレーサビリティ管理表 / 用語集 完成版 v1.0</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="18" customHeight="1">
+    <row r="15">
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>- 2026-05-中旬末 (予定): 全 8 件集約 + 正式版 v1.0 提出</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>- 2026-05-中旬末 (予定): 全 8 件集約 + 正式版 v1.0 提出</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/PLAN.md §5 Phase 計画 + 本書 §2 工程別進捗。</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
-        <is>
           <t>1.3 全体進捗概況</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="17">
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>最優先 4 件 (第 1 段階) のうち 2 件を確定し, 進捗率は 50% である。8 件全体では確定 2 件 + 骨格 1 件 (用語集) で進捗率は約 28% である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>用語規律 (受信者向け文書での内部用語使用禁止) は機械検査 (使用禁止語検査 + 採用語整合検査) と独立確認担当の人手判定の双方で確認しており, 確定済 2 件 (要件定義書 / 基本設計書) は使用禁止語ヒット 0 件である。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>最優先 4 件 (第 1 段階) のうち 2 件を確定し, 進捗率は 50% である。8 件全体では確定 2 件 + 骨格 1 件 (用語集) で進捗率は約 28% である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>用語規律 (受信者向け文書での内部用語使用禁止) は機械検査 (使用禁止語検査 + 採用語整合検査) と独立確認担当の人手判定の双方で確認しており, 確定済 2 件 (要件定義書 / 基本設計書) は使用禁止語ヒット 0 件である。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/glossary/research_reports/phase_1_04_term_audit_2026-04-29.md + phase_1_01_term_audit_2026-04-29.md。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
-        <is>
           <t>1.4 本中間版の同梱物</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+    <row r="20">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>本中間版 (zip パッケージ) には以下を同梱する。</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>- 04 要件定義書.xlsx (確定版 v1.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>- 01 基本設計書.xlsx (確定版 v1.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+    <row r="21">
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>- 01 要件定義書.xlsx (確定版 v1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>- 02 基本設計書.xlsx (確定版 v1.0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="18" t="inlineStr">
         <is>
           <t>- 07 進捗報告書.xlsx (本書, 中間版 v0.5)</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+    <row r="24">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>- 99 用語集.xlsx (骨格版 v0.1, 中国語列は仕上げ段階で充填)</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="17" t="inlineStr">
+    <row r="25">
+      <c r="C25" s="18" t="inlineStr">
         <is>
           <t>- 公開発布版資料 (ai_platforms/release/v1.0/) — 方法論・利用案内・既知制限事項を 3 言語で収録した参考資料</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>出典: docs/jp/deliverable/README_今回納品範囲.md。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -1332,7 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>0</t>
@@ -1364,39 +1312,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>用語調研</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>用語写像辞書 (33 項目) / 参照規格 16 件調査結果</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>独立確認担当による審査を 3 回実施し合格</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>0.7</t>
@@ -1428,39 +1376,39 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>0.5.8</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>用語集 骨格作成</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>99 用語集.xlsx (33 項目, 7 シート)</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>中国語列の充填は仕上げ段階で実施予定</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -1483,7 +1431,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>04 要件定義書.xlsx v1.0 (10 シート)</t>
+          <t>01 要件定義書.xlsx v1.0 (10 シート)</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -1492,39 +1440,39 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>1-2</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>基本設計書 起草 + 確定</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>01 基本設計書.xlsx v1.0 (10 シート)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
+        <is>
+          <t>02 基本設計書.xlsx v1.0 (10 シート)</t>
+        </is>
+      </c>
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>独立確認担当の審査 + 用語規律監査を経て無条件合格</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="18" customHeight="1">
+    <row r="9">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -1547,7 +1495,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02 運用保守マニュアル.xlsx (予定)</t>
+          <t>03 運用保守マニュアル.xlsx (予定)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -1556,39 +1504,39 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>1-4</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>試験結果報告書 起草</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D10" s="18" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E10" s="18" t="inlineStr">
+      <c r="E10" s="19" t="inlineStr">
         <is>
           <t>03 試験結果報告書.xlsx (予定)</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="19" t="inlineStr">
         <is>
           <t>第 1-3 と並列実施可能 (要件定義書の前提条件で試験範囲を画定)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
+    <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>2</t>
@@ -1620,39 +1568,39 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>3-1</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>トレーサビリティ管理表</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="18" t="inlineStr">
+      <c r="E12" s="19" t="inlineStr">
         <is>
           <t>06 トレーサビリティ管理表.xlsx (予定)</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="19" t="inlineStr">
         <is>
           <t>要件 ⇆ 設計 ⇆ 試験 ⇆ 証跡 横断表</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
+    <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -1684,39 +1632,39 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>3-3</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>進捗報告書 完成版</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>進行中</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D14" s="19" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E14" s="19" t="inlineStr">
         <is>
           <t>07 進捗報告書.xlsx 完成版</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="19" t="inlineStr">
         <is>
           <t>本中間版を更新する形で正式版 v1.0 に到達予定</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1">
+    <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
           <t>4</t>
@@ -1821,7 +1769,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>I-1</t>
@@ -1853,39 +1801,39 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>I-2</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>用語集 (99) の中国語列 33 行の充填</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>計画中</t>
         </is>
       </c>
-      <c r="E4" s="18" t="inlineStr">
+      <c r="E4" s="19" t="inlineStr">
         <is>
           <t>第 3 段階内</t>
         </is>
       </c>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>採用語確定後に一括充填予定. 中間版 (v0.5) では空欄表示で同梱</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>I-3</t>
@@ -1893,7 +1841,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>残最優先文書 (02 運用保守 + 03 試験結果) 着手</t>
+          <t>残最優先文書 (03 運用保守 + 04 試験結果) 着手</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
@@ -1917,33 +1865,33 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>I-4</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Excel 生成処理の作成日時固定化 (再現性向上)</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>計画中</t>
         </is>
       </c>
-      <c r="E6" s="18" t="inlineStr">
+      <c r="E6" s="19" t="inlineStr">
         <is>
           <t>第 3 段階内</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="19" t="inlineStr">
         <is>
           <t>同一入力での Excel ハッシュ完全一致を実現する補助改修 (内容には影響なし)</t>
         </is>
@@ -2010,7 +1958,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1">
+    <row r="3">
       <c r="A3" s="7" t="inlineStr">
         <is>
           <t>2026-05-01 〜 2026-05-03</t>
@@ -2018,7 +1966,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>02 運用保守マニュアル + 03 試験結果報告書 並列起草 + 独立確認</t>
+          <t>03 運用保守マニュアル + 03 試験結果報告書 並列起草 + 独立確認</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
@@ -2032,29 +1980,29 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="18" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
         <is>
           <t>2026-05-04 〜 2026-05-05</t>
         </is>
       </c>
-      <c r="B4" s="18" t="inlineStr">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>05 詳細設計書 起草 + 独立確認</t>
         </is>
       </c>
-      <c r="C4" s="18" t="inlineStr">
+      <c r="C4" s="19" t="inlineStr">
         <is>
           <t>05 v1.0</t>
         </is>
       </c>
-      <c r="D4" s="18" t="inlineStr">
+      <c r="D4" s="19" t="inlineStr">
         <is>
           <t>基本設計書 v1.0 の章別詳細展開</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="18" customHeight="1">
+    <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>2026-05-06 〜 2026-05-07</t>
@@ -2076,23 +2024,23 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>全 8 件集約 + 正式版 v1.0 zip 化 + 最終確認</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>正式版 v1.0 zip + 振り返り記録</t>
         </is>
       </c>
-      <c r="D6" s="18" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>全文書相互参照確認 / 機密区分 (公開可) 確認 / 受信者最終確認</t>
         </is>
@@ -2150,24 +2098,24 @@
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>04 要件定義書.xlsx (本中間版 同梱)</t>
-        </is>
-      </c>
-      <c r="B3" s="19" t="inlineStr">
-        <is>
-          <t>../04_要件定義書.xlsx</t>
+          <t>01 要件定義書.xlsx (本中間版 同梱)</t>
+        </is>
+      </c>
+      <c r="B3" s="20" t="inlineStr">
+        <is>
+          <t>../01_要件定義書.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>01 基本設計書.xlsx (本中間版 同梱)</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>../01_基本設計書.xlsx</t>
+          <t>02 基本設計書.xlsx (本中間版 同梱)</t>
+        </is>
+      </c>
+      <c r="B4" s="21" t="inlineStr">
+        <is>
+          <t>../02_基本設計書.xlsx</t>
         </is>
       </c>
     </row>
@@ -2177,7 +2125,7 @@
           <t>99 用語集.xlsx 骨格版 (本中間版 同梱)</t>
         </is>
       </c>
-      <c r="B5" s="19" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>../99_用語集.xlsx</t>
         </is>
@@ -2189,7 +2137,7 @@
           <t>公開発布版 README (日本語) — 方法論 / 利用案内 / 既知制限事項</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>../../ai_platforms/release/v1.0/README.ja.md</t>
         </is>
@@ -2201,7 +2149,7 @@
           <t>公開発布版 方法論 (日本語)</t>
         </is>
       </c>
-      <c r="B7" s="19" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>../../ai_platforms/release/v1.0/METHODOLOGY.ja.md</t>
         </is>
@@ -2213,7 +2161,7 @@
           <t>公開発布版 利用案内 (日本語)</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>../../ai_platforms/release/v1.0/USER_GUIDE.ja.md</t>
         </is>
@@ -2267,56 +2215,56 @@
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="21" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="B2" s="21" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>氏名</t>
         </is>
       </c>
-      <c r="C2" s="21" t="inlineStr">
+      <c r="C2" s="22" t="inlineStr">
         <is>
           <t>日付</t>
         </is>
       </c>
-      <c r="D2" s="21" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>押印・署名</t>
         </is>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>作成</t>
         </is>
       </c>
-      <c r="B3" s="23" t="n"/>
-      <c r="C3" s="23" t="n"/>
-      <c r="D3" s="23" t="n"/>
+      <c r="B3" s="24" t="n"/>
+      <c r="C3" s="24" t="n"/>
+      <c r="D3" s="24" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="25" t="inlineStr">
         <is>
           <t>確認</t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
     </row>
     <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>承認</t>
         </is>
       </c>
-      <c r="B5" s="23" t="n"/>
-      <c r="C5" s="23" t="n"/>
-      <c r="D5" s="23" t="n"/>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
